--- a/docs/pending.xlsx
+++ b/docs/pending.xlsx
@@ -2025,6 +2025,100 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing Site</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Landing page redesign completed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Run a full brand and conversion redesign later</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Product messaging and trust-signals upgraded</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rewrite positioning and supporting sections</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/pending.xlsx
+++ b/docs/pending.xlsx
@@ -1,9 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookViews>
-    <workbookView/>
-  </workbookViews>
   <sheets>
     <sheet name="Pending" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -15,7 +12,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +46,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Workspace Provisioning</t>
+          <t>Workspace Access</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Invite acceptance flow for seeded users implemented</t>
+          <t>Multi-workspace membership and org switching implemented</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -794,12 +790,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Stakeholder admins can be created, but acceptance/onboarding is not finished</t>
+          <t>Founder/support workflows will need to move across workspaces cleanly</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Build invite acceptance and completion flow</t>
+          <t>Design membership model and switcher</t>
         </is>
       </c>
     </row>
@@ -816,12 +812,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Workspace Access</t>
+          <t>Workspace Governance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Multi-workspace membership and org switching implemented</t>
+          <t>Workspace suspension, archive, and restore controls implemented</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -836,17 +832,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Founder/support workflows will need to move across workspaces cleanly</t>
+          <t>You need a lifecycle for dormant or non-compliant stakeholder orgs</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Design membership model and switcher</t>
+          <t>Add org status controls and UI</t>
         </is>
       </c>
     </row>
@@ -863,12 +859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Workspace Governance</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Workspace suspension, archive, and restore controls implemented</t>
+          <t>Org-level feature flags and lifecycle states implemented</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -888,12 +884,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>You need a lifecycle for dormant or non-compliant stakeholder orgs</t>
+          <t>Required for staged rollout and plan control</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Add org status controls and UI</t>
+          <t>Add feature flag and org state model</t>
         </is>
       </c>
     </row>
@@ -910,12 +906,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Org-level feature flags and lifecycle states implemented</t>
+          <t>Action-level RBAC matrix enforced across modules</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -930,39 +926,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Required for staged rollout and plan control</t>
+          <t>Current auth is stronger, but not yet a full action matrix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Add feature flag and org state model</t>
+          <t>Define and enforce per-action permissions</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phase 12</t>
+          <t>Phase 13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tenant Lifecycle</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Action-level RBAC matrix enforced across modules</t>
+          <t>Seat and entitlement model implemented</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -977,17 +973,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Current auth is stronger, but not yet a full action matrix</t>
+          <t>Stakeholder workspaces need plan-aware limits</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Define and enforce per-action permissions</t>
+          <t>Define seat model and enforcement</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1005,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Seat and entitlement model implemented</t>
+          <t>Billing and subscription admin console implemented</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1029,12 +1025,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Stakeholder workspaces need plan-aware limits</t>
+          <t>Admins need visibility into plan and seats</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Define seat model and enforcement</t>
+          <t>Build billing summary and controls</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1047,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Feature Gating</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Billing and subscription admin console implemented</t>
+          <t>Plan-aware feature gating implemented</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1076,12 +1072,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Admins need visibility into plan and seats</t>
+          <t>Needed to sell multiple tiers without code forks</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Build billing summary and controls</t>
+          <t>Add entitlements to routes and UI</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1094,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feature Gating</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plan-aware feature gating implemented</t>
+          <t>Trial, upgrade, and downgrade flows implemented</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1118,39 +1114,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needed to sell multiple tiers without code forks</t>
+          <t>Commercial readiness improves with self-service lifecycle</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Add entitlements to routes and UI</t>
+          <t>Add commercial lifecycle rules</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Phase 13</t>
+          <t>Phase 14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lifecycle</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Trial, upgrade, and downgrade flows implemented</t>
+          <t>Production error tracking and alerting configured</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1165,17 +1161,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Commercial readiness improves with self-service lifecycle</t>
+          <t>You should know when auth, AI, uploads, or DB fail in production</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Add commercial lifecycle rules</t>
+          <t>Configure monitoring and alerting</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1193,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Production error tracking and alerting configured</t>
+          <t>Structured logs and uptime monitoring configured</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1212,17 +1208,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>You should know when auth, AI, uploads, or DB fail in production</t>
+          <t>Support and operations need visibility into live failures</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Configure monitoring and alerting</t>
+          <t>Add log aggregation and uptime checks</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1235,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Async Work</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Structured logs and uptime monitoring configured</t>
+          <t>Background jobs and queue system implemented</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1264,12 +1260,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Support and operations need visibility into live failures</t>
+          <t>Digests, webhooks, and retries should not depend on request-response timing</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Add log aggregation and uptime checks</t>
+          <t>Add async job infrastructure</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1282,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Async Work</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Background jobs and queue system implemented</t>
+          <t>Backup and restore workflow documented and tested</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1306,17 +1302,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Digests, webhooks, and retries should not depend on request-response timing</t>
+          <t>Production data safety is not optional</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Add async job infrastructure</t>
+          <t>Define backup plan and run restore drills</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1334,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Backup and restore workflow documented and tested</t>
+          <t>Incident response runbook operationalized</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1353,39 +1349,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Production data safety is not optional</t>
+          <t>The docs exist, but the operating motion does not yet</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Define backup plan and run restore drills</t>
+          <t>Create and test response workflow</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Phase 14</t>
+          <t>Phase 15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Data Governance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Import/Export</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Incident response runbook operationalized</t>
+          <t>CSV importers for CRM, HR, inventory, and accounting implemented</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1405,12 +1401,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The docs exist, but the operating motion does not yet</t>
+          <t>Real customers will want to move data in fast</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Create and test response workflow</t>
+          <t>Build import tools and mapping UX</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1428,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CSV importers for CRM, HR, inventory, and accounting implemented</t>
+          <t>Admin export center for operational and compliance data implemented</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1452,12 +1448,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Real customers will want to move data in fast</t>
+          <t>Stakeholders will need consistent exports beyond isolated reports</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Build import tools and mapping UX</t>
+          <t>Add central export surface</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1470,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import/Export</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Admin export center for operational and compliance data implemented</t>
+          <t>Soft delete and record recovery flows implemented</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1499,12 +1495,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Stakeholders will need consistent exports beyond isolated reports</t>
+          <t>Accidental deletion without recovery will hurt trust</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Add central export surface</t>
+          <t>Add reversible delete patterns</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1517,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Soft delete and record recovery flows implemented</t>
+          <t>Data retention and purge controls implemented</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1546,12 +1542,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Accidental deletion without recovery will hurt trust</t>
+          <t>Needed for governance and NDPA discipline</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Add reversible delete patterns</t>
+          <t>Define retention policy and jobs</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1569,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Data retention and purge controls implemented</t>
+          <t>NDPA/privacy request workflow implemented</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1593,12 +1589,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needed for governance and NDPA discipline</t>
+          <t>Privacy requests should be operational, not only documented</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Define retention policy and jobs</t>
+          <t>Add request handling workflow</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1611,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NDPA/privacy request workflow implemented</t>
+          <t>Approval center for sensitive actions implemented</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1640,12 +1636,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Privacy requests should be operational, not only documented</t>
+          <t>High-risk actions need approvals and evidence</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Add request handling workflow</t>
+          <t>Build approval center and audit tie-in</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1658,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Approval center for sensitive actions implemented</t>
+          <t>White-label and enterprise branding controls implemented</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1682,39 +1678,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>High-risk actions need approvals and evidence</t>
+          <t>Important for polished stakeholder rollout, but not a launch blocker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Build approval center and audit tie-in</t>
+          <t>Add branding controls later</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phase 15</t>
+          <t>Phase 16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Data Governance</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>White-label and enterprise branding controls implemented</t>
+          <t>In-product help center and onboarding content implemented</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1734,12 +1730,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Important for polished stakeholder rollout, but not a launch blocker</t>
+          <t>Users need a support surface that does not depend on you manually answering everything</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Add branding controls later</t>
+          <t>Build help center and guides</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1752,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Support Ops</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>In-product help center and onboarding content implemented</t>
+          <t>Support impersonation with audit trail implemented</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1776,17 +1772,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Users need a support surface that does not depend on you manually answering everything</t>
+          <t>Support needs controlled access for troubleshooting</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Build help center and guides</t>
+          <t>Add audited impersonation or support sessions</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1799,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Support Ops</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Support impersonation with audit trail implemented</t>
+          <t>Customer usage and health analytics implemented</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1823,17 +1819,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Support needs controlled access for troubleshooting</t>
+          <t>Useful for renewals and stakeholder expansion</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Add audited impersonation or support sessions</t>
+          <t>Add adoption and health reporting</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1846,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Customer usage and health analytics implemented</t>
+          <t>Release notes and changelog workflow implemented</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Useful for renewals and stakeholder expansion</t>
+          <t>Customers should see product progress clearly</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Add adoption and health reporting</t>
+          <t>Add changelog discipline</t>
         </is>
       </c>
     </row>
@@ -1892,17 +1888,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Go-To-Market</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Release notes and changelog workflow implemented</t>
+          <t>Accessibility and mobile QA sweep completed</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1917,17 +1913,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Customers should see product progress clearly</t>
+          <t>Pitching stakeholders on unstable mobile/accessibility experiences is risky</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Add changelog discipline</t>
+          <t>Run QA sweep and fix findings</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1940,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Readiness</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accessibility and mobile QA sweep completed</t>
+          <t>Stakeholder pitch readiness gate completed</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1964,39 +1960,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pitching stakeholders on unstable mobile/accessibility experiences is risky</t>
+          <t>You need a formal go/no-go checklist before handing this to serious stakeholders</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Run QA sweep and fix findings</t>
+          <t>Use the pitch-readiness document as the gate</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Phase 16</t>
+          <t>Phase 17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Go-To-Market</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Readiness</t>
+          <t>Marketing Site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Stakeholder pitch readiness gate completed</t>
+          <t>Landing page redesign completed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2011,17 +2007,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>You need a formal go/no-go checklist before handing this to serious stakeholders</t>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Use the pitch-readiness document as the gate</t>
+          <t>Run a full brand and conversion redesign later</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2034,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Marketing Site</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Landing page redesign completed</t>
+          <t>Product messaging and trust-signals upgraded</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2063,57 +2059,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Current landing page is not yet strong enough for premium product positioning</t>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>Run a full brand and conversion redesign later</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Phase 17</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Positioning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Product messaging and trust-signals upgraded</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>Rewrite positioning and supporting sections</t>
         </is>
